--- a/data/nzd0483/nzd0483.xlsx
+++ b/data/nzd0483/nzd0483.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E567"/>
+  <dimension ref="A1:E570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12339,6 +12339,69 @@
         <v>373.44</v>
       </c>
       <c r="E567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>360.04</v>
+      </c>
+      <c r="C568" t="n">
+        <v>362.93</v>
+      </c>
+      <c r="D568" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>360.16</v>
+      </c>
+      <c r="C569" t="n">
+        <v>363.66</v>
+      </c>
+      <c r="D569" t="n">
+        <v>374.26</v>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>360.68</v>
+      </c>
+      <c r="C570" t="n">
+        <v>364.37</v>
+      </c>
+      <c r="D570" t="n">
+        <v>374.7</v>
+      </c>
+      <c r="E570" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12355,7 +12418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B731"/>
+  <dimension ref="A1:B734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19668,6 +19731,36 @@
       </c>
       <c r="B731" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -19836,28 +19929,28 @@
         <v>0.1368</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2923031598443848</v>
+        <v>-0.2975340560865473</v>
       </c>
       <c r="J2" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K2" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2049741459847265</v>
+        <v>0.2115129896238388</v>
       </c>
       <c r="M2" t="n">
-        <v>2.827177013023683</v>
+        <v>2.834690529249505</v>
       </c>
       <c r="N2" t="n">
-        <v>15.43177403679145</v>
+        <v>15.46224461197076</v>
       </c>
       <c r="O2" t="n">
-        <v>3.928329675166208</v>
+        <v>3.932206074453723</v>
       </c>
       <c r="P2" t="n">
-        <v>372.7808988389656</v>
+        <v>372.844535127601</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19918,28 +20011,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2376442671722434</v>
+        <v>-0.2413736760900727</v>
       </c>
       <c r="J3" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K3" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1991744644104925</v>
+        <v>0.2051481499022546</v>
       </c>
       <c r="M3" t="n">
-        <v>2.39416388167683</v>
+        <v>2.399636859267986</v>
       </c>
       <c r="N3" t="n">
-        <v>10.57366648089913</v>
+        <v>10.57645361136221</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25171746633977</v>
+        <v>3.252146000929573</v>
       </c>
       <c r="P3" t="n">
-        <v>373.3438458615012</v>
+        <v>373.3892099802348</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20000,28 +20093,28 @@
         <v>0.1107</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.239926031580296</v>
+        <v>-0.2409635573726333</v>
       </c>
       <c r="J4" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K4" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2410909140717893</v>
+        <v>0.2446519312693221</v>
       </c>
       <c r="M4" t="n">
-        <v>2.234831297060412</v>
+        <v>2.227100045167097</v>
       </c>
       <c r="N4" t="n">
-        <v>8.437821214131525</v>
+        <v>8.399295905972171</v>
       </c>
       <c r="O4" t="n">
-        <v>2.90479280055076</v>
+        <v>2.898153878932616</v>
       </c>
       <c r="P4" t="n">
-        <v>381.4897762016926</v>
+        <v>381.5023910643095</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20063,7 +20156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E567"/>
+  <dimension ref="A1:E570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35375,6 +35468,87 @@
         </is>
       </c>
     </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-45.35572145818959,170.8589896058627</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-45.35607594867582,170.85975405692318</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-45.356438860918686,170.86052304443226</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-45.35572059237703,170.85899052102155</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>-45.35607091358615,170.85976004034146</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>-45.356433287256166,170.86053047352974</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-45.35571684052253,170.8589944867096</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>-45.35606601644381,170.85976585982945</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>-45.356430402065946,170.86053431917958</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0483/nzd0483.xlsx
+++ b/data/nzd0483/nzd0483.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E570"/>
+  <dimension ref="A1:E572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12402,6 +12402,48 @@
         <v>374.7</v>
       </c>
       <c r="E570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>360.91</v>
+      </c>
+      <c r="C571" t="n">
+        <v>364.87</v>
+      </c>
+      <c r="D571" t="n">
+        <v>375.11</v>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>361.13</v>
+      </c>
+      <c r="C572" t="n">
+        <v>365.47</v>
+      </c>
+      <c r="D572" t="n">
+        <v>375.13</v>
+      </c>
+      <c r="E572" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12418,7 +12460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B734"/>
+  <dimension ref="A1:B736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19761,6 +19803,26 @@
       </c>
       <c r="B734" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -19929,28 +19991,28 @@
         <v>0.1368</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2975340560865473</v>
+        <v>-0.3003883526434747</v>
       </c>
       <c r="J2" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K2" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2115129896238388</v>
+        <v>0.2154562150971731</v>
       </c>
       <c r="M2" t="n">
-        <v>2.834690529249505</v>
+        <v>2.836961481908825</v>
       </c>
       <c r="N2" t="n">
-        <v>15.46224461197076</v>
+        <v>15.4581575426517</v>
       </c>
       <c r="O2" t="n">
-        <v>3.932206074453723</v>
+        <v>3.931686348458089</v>
       </c>
       <c r="P2" t="n">
-        <v>372.844535127601</v>
+        <v>372.8793850020443</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20011,28 +20073,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2413736760900727</v>
+        <v>-0.2426564045126046</v>
       </c>
       <c r="J3" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K3" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2051481499022546</v>
+        <v>0.2079745279149736</v>
       </c>
       <c r="M3" t="n">
-        <v>2.399636859267986</v>
+        <v>2.397454775853095</v>
       </c>
       <c r="N3" t="n">
-        <v>10.57645361136221</v>
+        <v>10.54984087733187</v>
       </c>
       <c r="O3" t="n">
-        <v>3.252146000929573</v>
+        <v>3.248051858781178</v>
       </c>
       <c r="P3" t="n">
-        <v>373.3892099802348</v>
+        <v>373.4048697004433</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20093,28 +20155,28 @@
         <v>0.1107</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2409635573726333</v>
+        <v>-0.2408773698608699</v>
       </c>
       <c r="J4" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K4" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2446519312693221</v>
+        <v>0.245931738260637</v>
       </c>
       <c r="M4" t="n">
-        <v>2.227100045167097</v>
+        <v>2.219763036536922</v>
       </c>
       <c r="N4" t="n">
-        <v>8.399295905972171</v>
+        <v>8.36992322453375</v>
       </c>
       <c r="O4" t="n">
-        <v>2.898153878932616</v>
+        <v>2.893081959525818</v>
       </c>
       <c r="P4" t="n">
-        <v>381.5023910643095</v>
+        <v>381.5013385710694</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20156,7 +20218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E570"/>
+  <dimension ref="A1:E572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35549,6 +35611,60 @@
         </is>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-45.35571518104838,170.8589962407638</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>-45.35606256775183,170.8597699580598</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>-45.356427713593135,170.8605379026257</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-45.35571359372526,170.85899791855462</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-45.356058429321244,170.85977487593559</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-45.35642758244813,170.86053807742795</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0483/nzd0483.xlsx
+++ b/data/nzd0483/nzd0483.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E572"/>
+  <dimension ref="A1:E574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12444,6 +12444,48 @@
         <v>375.13</v>
       </c>
       <c r="E572" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>361.34</v>
+      </c>
+      <c r="C573" t="n">
+        <v>365.42</v>
+      </c>
+      <c r="D573" t="n">
+        <v>374.93</v>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>362.46</v>
+      </c>
+      <c r="C574" t="n">
+        <v>367.89</v>
+      </c>
+      <c r="D574" t="n">
+        <v>376.46</v>
+      </c>
+      <c r="E574" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12460,7 +12502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B736"/>
+  <dimension ref="A1:B739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19823,6 +19865,36 @@
       </c>
       <c r="B736" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -19991,28 +20063,28 @@
         <v>0.1368</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3003883526434747</v>
+        <v>-0.3025238564559832</v>
       </c>
       <c r="J2" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K2" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2154562150971731</v>
+        <v>0.2188403290184227</v>
       </c>
       <c r="M2" t="n">
-        <v>2.836961481908825</v>
+        <v>2.836086839221741</v>
       </c>
       <c r="N2" t="n">
-        <v>15.4581575426517</v>
+        <v>15.43347822914848</v>
       </c>
       <c r="O2" t="n">
-        <v>3.931686348458089</v>
+        <v>3.928546579735116</v>
       </c>
       <c r="P2" t="n">
-        <v>372.8793850020443</v>
+        <v>372.905527985416</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20073,28 +20145,28 @@
         <v>0.0701</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2426564045126046</v>
+        <v>-0.2427944226921451</v>
       </c>
       <c r="J3" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K3" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2079745279149736</v>
+        <v>0.2093369448632156</v>
       </c>
       <c r="M3" t="n">
-        <v>2.397454775853095</v>
+        <v>2.393452783459864</v>
       </c>
       <c r="N3" t="n">
-        <v>10.54984087733187</v>
+        <v>10.51853072651241</v>
       </c>
       <c r="O3" t="n">
-        <v>3.248051858781178</v>
+        <v>3.243228441925178</v>
       </c>
       <c r="P3" t="n">
-        <v>373.4048697004433</v>
+        <v>373.4065456793932</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20155,28 +20227,28 @@
         <v>0.1107</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2408773698608699</v>
+        <v>-0.2403445921872734</v>
       </c>
       <c r="J4" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K4" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L4" t="n">
-        <v>0.245931738260637</v>
+        <v>0.2464421825979664</v>
       </c>
       <c r="M4" t="n">
-        <v>2.219763036536922</v>
+        <v>2.215099688573096</v>
       </c>
       <c r="N4" t="n">
-        <v>8.36992322453375</v>
+        <v>8.344538941734038</v>
       </c>
       <c r="O4" t="n">
-        <v>2.893081959525818</v>
+        <v>2.8886915622361</v>
       </c>
       <c r="P4" t="n">
-        <v>381.5013385710694</v>
+        <v>381.4948058894997</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20218,7 +20290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E572"/>
+  <dimension ref="A1:E574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35665,6 +35737,60 @@
         </is>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>-45.35571207855316,170.85899952008214</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>-45.35605877419047,170.85977446611264</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>-45.35642889389829,170.8605363294055</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>-45.35570399763486,170.85900806156087</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>-45.35604173764889,170.85979471136056</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>-45.35641886130373,170.86054970177517</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
